--- a/sample-data/bugs_export.xlsx
+++ b/sample-data/bugs_export.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>R-2026.4</t>
+          <t>V8.3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R-2026.4</t>
+          <t>V8.3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
